--- a/Side Bar Files/GWD Data/HP Repair Spares.xlsx
+++ b/Side Bar Files/GWD Data/HP Repair Spares.xlsx
@@ -321,8 +321,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -719,7 +723,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC81B934-676D-4DBF-9F5A-6FE2F66AB9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52E608D4-1867-42EA-BA02-F4618568B9A7}">
   <dimension ref="A1:D58"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/HP Repair Spares.xlsx
+++ b/Side Bar Files/GWD Data/HP Repair Spares.xlsx
@@ -291,25 +291,11 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -342,11 +328,11 @@
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -723,7 +709,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52E608D4-1867-42EA-BA02-F4618568B9A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A424F63-B403-4803-B1D8-058FCFFCBAA6}">
   <dimension ref="A1:D58"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/HP Repair Spares.xlsx
+++ b/Side Bar Files/GWD Data/HP Repair Spares.xlsx
@@ -709,7 +709,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A424F63-B403-4803-B1D8-058FCFFCBAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D159FD5-99F2-4114-8D3E-C2014374BAA6}">
   <dimension ref="A1:D58"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/HP Repair Spares.xlsx
+++ b/Side Bar Files/GWD Data/HP Repair Spares.xlsx
@@ -709,7 +709,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D159FD5-99F2-4114-8D3E-C2014374BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06138C1F-18BD-4F07-9AEF-186D7E1CBAA6}">
   <dimension ref="A1:D58"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
